--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,11 +434,6 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ts</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>version</t>
         </is>
       </c>
@@ -459,11 +454,6 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-01-15 08:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>XL-001</t>
         </is>
       </c>
@@ -484,11 +474,6 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-01-15 10:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>XL-002</t>
         </is>
       </c>
@@ -509,11 +494,6 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-01-15 03:00:00+00:00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>XL-003</t>
         </is>
       </c>
@@ -534,11 +514,6 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-01-15 06:30:00+00:00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>XL-004</t>
         </is>
       </c>
@@ -559,11 +534,6 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-01-15 10:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>XL-005</t>
         </is>
       </c>
@@ -584,11 +554,6 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-01-15 13:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>XL-006</t>
         </is>
       </c>
@@ -609,11 +574,6 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024-01-15 12:15:00+05:30</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>XL-007</t>
         </is>
       </c>
@@ -634,11 +594,6 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024-01-15 14:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>XL-008</t>
         </is>
       </c>
@@ -659,11 +614,6 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024-01-15 13:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>XL-009</t>
         </is>
       </c>
@@ -684,11 +634,6 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024-01-15 07:45:00+00:00</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>XL-010</t>
         </is>
       </c>
@@ -709,11 +654,6 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024-01-15 12:45:00+05:30</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>XL-011</t>
         </is>
       </c>
@@ -733,11 +673,6 @@
         <v>93</v>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>2024-01-15 11:15:00+05:30</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>XL-012</t>
         </is>
